--- a/17-06-26/Furqan.xlsx
+++ b/17-06-26/Furqan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D437042-4F93-4D8D-B1E6-8B3786D3BC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B1F1AF-D4E5-4732-9D15-760C4B5E184F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3369,7 +3369,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3397,7 +3397,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4590,7 +4590,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4618,7 +4618,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5811,7 +5811,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5839,7 +5839,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7032,7 +7032,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7060,7 +7060,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8253,7 +8253,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8281,7 +8281,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9474,7 +9474,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9502,7 +9502,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10692,7 +10692,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10720,7 +10720,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11909,7 +11909,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11937,7 +11937,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13126,7 +13126,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13154,7 +13154,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14343,7 +14343,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14371,7 +14371,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18310,7 +18310,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18338,7 +18338,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19527,7 +19527,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19555,7 +19555,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20744,7 +20744,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20772,7 +20772,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21961,7 +21961,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -21989,7 +21989,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23183,7 +23183,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23211,7 +23211,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23475,7 +23475,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>7170.9962985000002</v>
+        <v>6862.2397965</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23524,23 +23524,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>277.00199999999995</v>
+        <v>360.94200000000001</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>3185.5230000000001</v>
+        <v>3101.5830000000001</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>723.85658999999998</v>
+        <v>705.38979000000006</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>26.38129275</v>
+        <v>25.86925875</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>3935.7608827499998</v>
+        <v>3832.8420487500002</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'4'!P35</f>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23598,23 +23598,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>277.00199999999995</v>
+        <v>360.94200000000001</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>3185.5230000000001</v>
+        <v>3101.5830000000001</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>723.85658999999998</v>
+        <v>705.38979000000006</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>26.38129275</v>
+        <v>25.86925875</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>3935.7608827499998</v>
+        <v>3832.8420487500002</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23672,23 +23672,23 @@
       </c>
       <c r="L18" s="175">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>167.88</v>
+        <v>251.82</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="2"/>
-        <v>1930.62</v>
+        <v>1846.68</v>
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>447.81990000000002</v>
+        <v>429.35310000000004</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>11.8921995</v>
+        <v>11.3801655</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>2390.3320994999999</v>
+        <v>2287.4132655000003</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23726,15 +23726,15 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>3486.7200000000003</v>
+        <v>581.12</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
@@ -23742,23 +23742,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>278.93760000000003</v>
+        <v>46.489600000000003</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>3207.7824000000001</v>
+        <v>534.63040000000001</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>737.67372799999998</v>
+        <v>117.61868800000001</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>98.636403200000018</v>
+        <v>16.306227200000002</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>4044.0925311999999</v>
+        <v>668.5553152</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23766,7 +23766,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>6751.0744320000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23866,15 +23866,15 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>3414.08</v>
+        <v>508.48</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="172">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
@@ -23882,23 +23882,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>273.12639999999999</v>
+        <v>40.678400000000003</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>3140.9535999999998</v>
+        <v>467.80160000000001</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>722.97139199999992</v>
+        <v>102.916352</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>96.598124800000008</v>
+        <v>14.267948799999999</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>3960.5231167999996</v>
+        <v>584.98590079999997</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23936,11 +23936,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>1176.9000000000001</v>
+        <v>941.5200000000001</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -23948,27 +23948,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>41.191500000000012</v>
+        <v>32.95320000000001</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>58.845000000000013</v>
+        <v>47.076000000000008</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>1076.8635000000002</v>
+        <v>861.49080000000004</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>202.45033799999999</v>
+        <v>155.068344</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>31.982845950000005</v>
+        <v>25.413978600000004</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>1311.29668395</v>
+        <v>1041.9731226000001</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24126,7 +24126,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>7.55</v>
+        <v>5.4</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24137,39 +24137,39 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>302</v>
+        <v>216</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>17464.45</v>
+        <v>11417.87</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>41.191500000000012</v>
+        <v>32.95320000000001</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1361.8489999999999</v>
+        <v>1137.0039999999999</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>16061.409500000002</v>
+        <v>10247.9128</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>3648.1210179999998</v>
+        <v>2305.2285440000001</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>302.46307095000003</v>
+        <v>129.69774960000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>20011.993588950001</v>
+        <v>12682.839093600001</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>20011.993588950001</v>
+        <v>12682.8390936</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24332,7 +24332,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>17464.45</v>
+        <v>11417.87</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24353,7 +24353,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>1361.8489999999999</v>
+        <v>1137.0039999999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24374,7 +24374,7 @@
       <c r="O34" s="240"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>41.191500000000012</v>
+        <v>32.95320000000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24396,7 +24396,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>16061.4095</v>
+        <v>10247.912800000002</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24421,7 +24421,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>3648.1210179999998</v>
+        <v>2305.2285440000001</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24443,7 +24443,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>19709.530518</v>
+        <v>12553.141344000001</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>492.73826295000003</v>
+        <v>313.82853360000007</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24478,7 +24478,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>20202.268780949998</v>
+        <v>12866.969877600002</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24558,7 +24558,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
@@ -24650,7 +24650,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24678,7 +24678,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25877,7 +25877,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25905,7 +25905,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -26214,24 +26214,24 @@
         <v>0</v>
       </c>
       <c r="L16" s="105">
-        <f>I16*8%</f>
-        <v>167.88</v>
+        <f>I16*12%</f>
+        <v>251.82</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1930.62</v>
+        <v>1846.68</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>447.81990000000002</v>
+        <v>429.35310000000004</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>11.8921995</v>
+        <v>11.3801655</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>2390.3320994999999</v>
+        <v>2287.4132655000003</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -26278,24 +26278,24 @@
         <v>0</v>
       </c>
       <c r="L17" s="105">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>167.88</v>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
+        <v>251.82</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>1930.62</v>
+        <v>1846.68</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>447.81990000000002</v>
+        <v>429.35310000000004</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>11.8921995</v>
+        <v>11.3801655</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>2390.3320994999999</v>
+        <v>2287.4132655000003</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -26343,23 +26343,23 @@
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>167.88</v>
+        <v>251.82</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>1930.62</v>
+        <v>1846.68</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>447.81990000000002</v>
+        <v>429.35310000000004</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>11.8921995</v>
+        <v>11.3801655</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>2390.3320994999999</v>
+        <v>2287.4132655000003</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26726,23 +26726,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>503.64</v>
+        <v>755.46</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>5791.86</v>
+        <v>5540.04</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1343.4597000000001</v>
+        <v>1288.0593000000001</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>35.676598499999997</v>
+        <v>34.140496499999998</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>7170.9962985000002</v>
+        <v>6862.2397965000009</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26813,7 +26813,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>503.64</v>
+        <v>755.46</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26856,7 +26856,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>5791.86</v>
+        <v>5540.04</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26881,7 +26881,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1343.4597000000001</v>
+        <v>1288.0593000000001</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26903,7 +26903,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>7135.3197</v>
+        <v>6828.0992999999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>35.676598500000004</v>
+        <v>34.140496499999998</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26938,7 +26938,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>7170.9962985000002</v>
+        <v>6862.2397965</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27110,7 +27110,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27138,7 +27138,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28338,7 +28338,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28366,7 +28366,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29004,37 +29004,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>6</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>6.5688673500000014</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" hidden="1" x14ac:dyDescent="0.35">
@@ -29164,36 +29162,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>6.5688673500000014</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29243,7 +29241,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>235.38000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29264,7 +29262,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>11.769000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29285,7 +29283,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>8.2383000000000024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29307,7 +29305,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>215.37270000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29332,7 +29330,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>47.381993999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29354,7 +29352,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>262.75469400000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29379,7 +29377,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>6.5688673500000014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29389,7 +29387,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>269.32356135000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29561,7 +29559,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29589,7 +29587,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -30790,7 +30788,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30818,7 +30816,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -31288,39 +31286,35 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>40</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>2905.6</v>
-      </c>
-      <c r="J19" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="117"/>
       <c r="K19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>232.44800000000001</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>2673.152</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>620.05503999999996</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>82.330176000000009</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>3375.5372160000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31404,39 +31398,35 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>40</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>2905.6</v>
-      </c>
-      <c r="J21" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" s="117"/>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>232.44800000000001</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>2673.152</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>620.05503999999996</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>82.330176000000009</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>3375.5372160000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31622,11 +31612,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -31635,23 +31625,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>5346.3040000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1240.1100799999999</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>164.66035200000002</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>6751.0744320000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31701,7 +31691,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>5811.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31722,7 +31712,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>464.89600000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31765,7 +31755,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>5346.3040000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31790,7 +31780,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1240.1100799999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31812,7 +31802,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>6586.4140800000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31837,7 +31827,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>164.66035200000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31847,7 +31837,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>6751.0744320000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
